--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104628_W19.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104628_W19.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.3472</v>
+        <v>9.955399999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>7.587</v>
+        <v>7.4393</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7602</v>
+        <v>2.5161</v>
       </c>
       <c r="G2" t="n">
-        <v>7.1222</v>
+        <v>7.1319</v>
       </c>
       <c r="H2" t="n">
-        <v>2.5481</v>
+        <v>2.5557</v>
       </c>
       <c r="I2" t="n">
-        <v>4.5741</v>
+        <v>4.5762</v>
       </c>
       <c r="J2" t="n">
-        <v>6.9233</v>
+        <v>6.9008</v>
       </c>
       <c r="K2" t="n">
-        <v>3.117</v>
+        <v>3.1026</v>
       </c>
       <c r="L2" t="n">
-        <v>3.8063</v>
+        <v>3.7982</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1989</v>
+        <v>0.2311</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5689</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7678</v>
+        <v>0.778</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0643</v>
+        <v>0.6657</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5444</v>
+        <v>0.4294</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5199</v>
+        <v>0.2363</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.6591</v>
+        <v>6.1567</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9855</v>
+        <v>5.359</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6736</v>
+        <v>0.7977</v>
       </c>
       <c r="G3" t="n">
-        <v>4.878</v>
+        <v>4.8684</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5036</v>
+        <v>-0.5027</v>
       </c>
       <c r="I3" t="n">
-        <v>5.3816</v>
+        <v>5.3711</v>
       </c>
       <c r="J3" t="n">
-        <v>5.6764</v>
+        <v>5.6401</v>
       </c>
       <c r="K3" t="n">
-        <v>0.159</v>
+        <v>0.1444</v>
       </c>
       <c r="L3" t="n">
-        <v>5.5175</v>
+        <v>5.4957</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7984</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6626</v>
+        <v>-0.6471</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1359</v>
+        <v>-0.1246</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4969</v>
+        <v>0.0199</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3811</v>
+        <v>0.0439</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1159</v>
+        <v>-0.024</v>
       </c>
       <c r="V3" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.1028</v>
+        <v>5.1406</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3294</v>
+        <v>3.717</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7734</v>
+        <v>1.4236</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0813</v>
+        <v>3.0832</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4877</v>
+        <v>0.4882</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5936</v>
+        <v>2.595</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3579</v>
+        <v>2.3337</v>
       </c>
       <c r="K4" t="n">
-        <v>0.159</v>
+        <v>0.1444</v>
       </c>
       <c r="L4" t="n">
-        <v>2.199</v>
+        <v>2.1893</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7233000000000001</v>
+        <v>0.7495000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3288</v>
+        <v>0.3438</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3946</v>
+        <v>0.4057</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4833</v>
+        <v>-0.4387</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6261</v>
+        <v>-0.2023</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1427</v>
+        <v>-0.2364</v>
       </c>
       <c r="V4" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="W4" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.006</v>
+        <v>3.2435</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5831</v>
+        <v>1.5017</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4229</v>
+        <v>1.7418</v>
       </c>
       <c r="G5" t="n">
-        <v>3.4805</v>
+        <v>3.4861</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1513</v>
+        <v>0.1631</v>
       </c>
       <c r="I5" t="n">
-        <v>3.3292</v>
+        <v>3.3231</v>
       </c>
       <c r="J5" t="n">
-        <v>4.0389</v>
+        <v>4.0129</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2007</v>
+        <v>0.1929</v>
       </c>
       <c r="L5" t="n">
-        <v>3.8382</v>
+        <v>3.8201</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5584</v>
+        <v>-0.5268</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0494</v>
+        <v>-0.0298</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.509</v>
+        <v>-0.497</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R5" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4745</v>
+        <v>-0.2426</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2662</v>
+        <v>0.2203</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7407</v>
+        <v>-0.4629</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.6127</v>
+        <v>2.4887</v>
       </c>
       <c r="E6" t="n">
-        <v>2.3613</v>
+        <v>2.1732</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2514</v>
+        <v>0.3155</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5534</v>
+        <v>1.5577</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7879</v>
+        <v>1.7838</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6346</v>
+        <v>2.6164</v>
       </c>
       <c r="K6" t="n">
-        <v>2.2614</v>
+        <v>2.244</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3732</v>
+        <v>0.3724</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0812</v>
+        <v>-1.0587</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4735</v>
+        <v>-0.4603</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6077</v>
+        <v>-0.5984</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5622</v>
+        <v>0.4286</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4053</v>
+        <v>0.2413</v>
       </c>
       <c r="U6" t="n">
-        <v>0.157</v>
+        <v>0.1873</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.3176</v>
+        <v>-1.3187</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. KHATIASHVILI</t>
+          <t>K. SIMMONS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9912</v>
+        <v>2.4365</v>
       </c>
       <c r="E7" t="n">
-        <v>2.2578</v>
+        <v>1.5595</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2666</v>
+        <v>0.877</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4029</v>
+        <v>2.6627</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2338</v>
+        <v>1.5905</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.6366</v>
+        <v>1.0722</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9534</v>
+        <v>2.0579</v>
       </c>
       <c r="K7" t="n">
-        <v>1.6278</v>
+        <v>1.4479</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6744</v>
+        <v>0.61</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3563</v>
+        <v>0.6048</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.394</v>
+        <v>0.1426</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9622000000000001</v>
+        <v>0.4622</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9073</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2268</v>
+        <v>-3.4145</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S7" t="n">
-        <v>0.008500000000000001</v>
+        <v>-0.8313</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4386</v>
+        <v>0.0346</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4301</v>
+        <v>-0.8659</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4783</v>
+        <v>2.8814</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0927</v>
+        <v>2.8814</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. SIMMONS</t>
+          <t>M. KHATIASHVILI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8024</v>
+        <v>1.8171</v>
       </c>
       <c r="E8" t="n">
-        <v>1.0143</v>
+        <v>2.0084</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7881</v>
+        <v>-0.1913</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6579</v>
+        <v>-0.4049</v>
       </c>
       <c r="H8" t="n">
-        <v>1.5784</v>
+        <v>1.2322</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0795</v>
+        <v>-1.6371</v>
       </c>
       <c r="J8" t="n">
-        <v>2.0809</v>
+        <v>0.9423</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4546</v>
+        <v>1.6203</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6263</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>0.577</v>
+        <v>-1.3472</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1238</v>
+        <v>-0.3881</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4532</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.2683</v>
+        <v>0.9105</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.4025</v>
+        <v>-0.2276</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.4796</v>
+        <v>-0.165</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5565</v>
+        <v>0.2042</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9231</v>
+        <v>-0.3692</v>
       </c>
       <c r="V8" t="n">
-        <v>2.8924</v>
+        <v>1.4764</v>
       </c>
       <c r="W8" t="n">
-        <v>2.8924</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3448</v>
+        <v>1.796</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2036</v>
+        <v>0.527</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1412</v>
+        <v>1.269</v>
       </c>
       <c r="G9" t="n">
-        <v>3.8106</v>
+        <v>3.822</v>
       </c>
       <c r="H9" t="n">
-        <v>1.1557</v>
+        <v>1.1628</v>
       </c>
       <c r="I9" t="n">
-        <v>2.6549</v>
+        <v>2.6592</v>
       </c>
       <c r="J9" t="n">
-        <v>4.0468</v>
+        <v>4.0345</v>
       </c>
       <c r="K9" t="n">
-        <v>1.4719</v>
+        <v>1.4651</v>
       </c>
       <c r="L9" t="n">
-        <v>2.5749</v>
+        <v>2.5693</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2362</v>
+        <v>-0.2125</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3162</v>
+        <v>-0.3023</v>
       </c>
       <c r="O9" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.7635</v>
+        <v>-4.7803</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2882</v>
+        <v>0.1593</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1724</v>
+        <v>0.1833</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1159</v>
+        <v>-0.024</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.055</v>
+        <v>-0.2348</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4601</v>
+        <v>-0.0801</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4052</v>
+        <v>-0.1547</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4899</v>
+        <v>-0.4825</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4457</v>
+        <v>0.4561</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9356</v>
+        <v>-0.9386</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3474</v>
+        <v>-0.3701</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6682</v>
+        <v>0.6583</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.0157</v>
+        <v>-1.0284</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1425</v>
+        <v>-0.1124</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2225</v>
+        <v>-0.2022</v>
       </c>
       <c r="O10" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2017</v>
+        <v>-0.5051</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8075</v>
+        <v>0.29</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0093</v>
+        <v>-0.7951</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1394</v>
+        <v>-0.3365</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.5481</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8233</v>
+        <v>-0.8845</v>
       </c>
       <c r="G11" t="n">
-        <v>1.3335</v>
+        <v>1.3485</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2033</v>
+        <v>0.2148</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1302</v>
+        <v>1.1338</v>
       </c>
       <c r="J11" t="n">
-        <v>0.426</v>
+        <v>0.4135</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.09370000000000001</v>
+        <v>-0.1002</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>0.9074</v>
+        <v>0.9351</v>
       </c>
       <c r="N11" t="n">
-        <v>0.297</v>
+        <v>0.3149</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6105</v>
+        <v>0.6201</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3802</v>
+        <v>-0.5955</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2994</v>
+        <v>0.1833</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6796</v>
+        <v>-0.7788</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.4803</v>
+        <v>-1.9215</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5760999999999999</v>
+        <v>0.213</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0564</v>
+        <v>-2.1345</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3201</v>
+        <v>-0.3186</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9567</v>
+        <v>0.9564</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.2768</v>
+        <v>-1.275</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0448</v>
+        <v>0.0377</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8312</v>
+        <v>0.8274</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3649</v>
+        <v>-0.3563</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1255</v>
+        <v>0.129</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2519</v>
+        <v>-0.1963</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4386</v>
+        <v>0.0858</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1866</v>
+        <v>-0.2821</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.999</v>
+        <v>-2.887</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.6673</v>
+        <v>-1.5633</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.3317</v>
+        <v>-1.3237</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.0867</v>
+        <v>-3.0936</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.554</v>
+        <v>-1.5593</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.5327</v>
+        <v>-1.5344</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.3244</v>
+        <v>-2.3345</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.5381</v>
+        <v>-1.5448</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.7622</v>
+        <v>-0.7592</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0159</v>
+        <v>-0.0144</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.7463</v>
+        <v>-0.7447</v>
       </c>
       <c r="P13" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R13" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.366</v>
+        <v>-0.2486</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2087</v>
+        <v>-0.0907</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1573</v>
+        <v>-0.1579</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>27.3025</v>
+        <v>27.65469999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>23.3749</v>
+        <v>23.40280000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>3.9276</v>
+        <v>4.251999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>23.6178</v>
+        <v>23.6609</v>
       </c>
       <c r="H14" t="n">
-        <v>8.491</v>
+        <v>8.541599999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>15.1269</v>
+        <v>15.1195</v>
       </c>
       <c r="J14" t="n">
-        <v>26.5112</v>
+        <v>26.2852</v>
       </c>
       <c r="K14" t="n">
-        <v>10.319</v>
+        <v>10.2023</v>
       </c>
       <c r="L14" t="n">
-        <v>16.1922</v>
+        <v>16.0831</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.8935</v>
+        <v>-2.6243</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.8279</v>
+        <v>-1.6608</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.0654</v>
+        <v>-0.9637</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.1341</v>
+        <v>-1.1381</v>
       </c>
       <c r="Q14" t="n">
-        <v>-18.1468</v>
+        <v>-18.2107</v>
       </c>
       <c r="R14" t="n">
-        <v>17.0125</v>
+        <v>17.0725</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.2835</v>
+        <v>-1.9496</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2552</v>
+        <v>1.6231</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.5389</v>
+        <v>-3.572700000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>7.102299999999999</v>
+        <v>7.081300000000002</v>
       </c>
       <c r="W14" t="n">
-        <v>13.755</v>
+        <v>13.7047</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.6525</v>
+        <v>-6.6231</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.7968</v>
+        <v>4.2695</v>
       </c>
       <c r="E15" t="n">
-        <v>3.9813</v>
+        <v>3.6985</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8155</v>
+        <v>0.571</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.4048</v>
+        <v>-1.4162</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7276</v>
+        <v>0.7076</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.1324</v>
+        <v>-2.1238</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4654</v>
+        <v>0.4293</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0279</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5625</v>
+        <v>-0.5662</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.8702</v>
+        <v>-1.8455</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3003</v>
+        <v>-0.2879</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.5699</v>
+        <v>-1.5576</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3274</v>
+        <v>0.8141</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8257</v>
+        <v>0.5942</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5017</v>
+        <v>0.22</v>
       </c>
       <c r="V15" t="n">
-        <v>3.0595</v>
+        <v>3.0505</v>
       </c>
       <c r="W15" t="n">
-        <v>3.8243</v>
+        <v>3.8132</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.7649</v>
+        <v>-0.7625999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>J. WRIGHT-FOREMAN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9191</v>
+        <v>-0.048</v>
       </c>
       <c r="E16" t="n">
-        <v>3.2933</v>
+        <v>2.0047</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.3742</v>
+        <v>-2.0527</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.0312</v>
+        <v>0.8018999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8687</v>
+        <v>-0.8441</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1626</v>
+        <v>1.6461</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1031</v>
+        <v>3.3661</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1283</v>
+        <v>-0.0969</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2315</v>
+        <v>3.463</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.1344</v>
+        <v>-2.5642</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.7472</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.394</v>
+        <v>-1.8169</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9073</v>
+        <v>0.6829</v>
       </c>
       <c r="Q16" t="n">
+        <v>-1.1382</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.8211</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-0.2254</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.2232</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-1.3074</v>
+      </c>
+      <c r="W16" t="n">
         <v>0</v>
       </c>
-      <c r="R16" t="n">
-        <v>0.9073</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.975</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.0294</v>
-      </c>
-      <c r="U16" t="n">
-        <v>-0.0544</v>
-      </c>
-      <c r="V16" t="n">
-        <v>-0.9320000000000001</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0.1607</v>
-      </c>
       <c r="X16" t="n">
-        <v>-1.0927</v>
+        <v>-1.3074</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. KOUMADJE</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8246</v>
+        <v>-0.1305</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6161</v>
+        <v>2.2249</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.4406</v>
+        <v>-2.3554</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1338</v>
+        <v>-1.0267</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9063</v>
+        <v>-0.8673999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.7725</v>
+        <v>-0.1592</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7673</v>
+        <v>1.0942</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6553</v>
+        <v>-0.1346</v>
       </c>
       <c r="L17" t="n">
-        <v>0.112</v>
+        <v>1.2288</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6335</v>
+        <v>-2.1209</v>
       </c>
       <c r="N17" t="n">
-        <v>0.251</v>
+        <v>-0.7328</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.8844</v>
+        <v>-1.3881</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="S17" t="n">
-        <v>1.8065</v>
+        <v>0.9173</v>
       </c>
       <c r="T17" t="n">
-        <v>2.1171</v>
+        <v>0.9729</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3106</v>
+        <v>-0.0556</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.8575</v>
+        <v>-0.9317</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.8575</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.865</v>
+        <v>-0.8355</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0968</v>
+        <v>-1.1009</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2318</v>
+        <v>0.2655</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0214</v>
+        <v>0.0228</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0159</v>
+        <v>-0.0144</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0159</v>
+        <v>-0.0144</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0159</v>
+        <v>-0.0144</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0209</v>
+        <v>0.0523</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0209</v>
+        <v>0.0523</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. WRIGHT-FOREMAN</t>
+          <t>J. RODRIGUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0253</v>
+        <v>-1.7658</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5572</v>
+        <v>0.5167</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.5825</v>
+        <v>-2.2825</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8048999999999999</v>
+        <v>-1.0362</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8397</v>
+        <v>-2.1905</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6446</v>
+        <v>1.1543</v>
       </c>
       <c r="J19" t="n">
-        <v>3.387</v>
+        <v>1.6567</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.0835</v>
+        <v>-0.8973</v>
       </c>
       <c r="L19" t="n">
-        <v>3.4705</v>
+        <v>2.554</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.5821</v>
+        <v>-2.6929</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7563</v>
+        <v>-1.2932</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.8258</v>
+        <v>-1.3997</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1995</v>
+        <v>0.2217</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6956</v>
+        <v>0.3851</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5039</v>
+        <v>-0.1634</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.3112</v>
+        <v>-1.6342</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.387</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.3112</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. GONZALEZ</t>
+          <t>C. KOUMADJE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8589</v>
+        <v>-2.0112</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3379</v>
+        <v>0.182</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.1967</v>
+        <v>-2.1932</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.2416</v>
+        <v>0.1371</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.525</v>
+        <v>1.8989</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.7166</v>
+        <v>-1.7617</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0655</v>
+        <v>1.7525</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2384</v>
+        <v>1.6408</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.3039</v>
+        <v>0.1117</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.1761</v>
+        <v>-1.6154</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.7635</v>
+        <v>0.2581</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.4126</v>
+        <v>-1.8734</v>
       </c>
       <c r="P20" t="n">
-        <v>1.361</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R20" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2751</v>
+        <v>0.6143</v>
       </c>
       <c r="T20" t="n">
-        <v>1.4034</v>
+        <v>0.7058</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1282</v>
+        <v>-0.0915</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2534</v>
+        <v>-1.8521</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2534</v>
+        <v>-1.8521</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ</t>
+          <t>M. GONZALEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1546</v>
+        <v>-2.5522</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6155</v>
+        <v>0.4859</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.5391</v>
+        <v>-3.0381</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.0175</v>
+        <v>-3.2489</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.1743</v>
+        <v>-1.536</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1568</v>
+        <v>-1.7129</v>
       </c>
       <c r="J21" t="n">
-        <v>1.7027</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.8667</v>
+        <v>0.2166</v>
       </c>
       <c r="L21" t="n">
-        <v>2.5694</v>
+        <v>-0.3132</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.7202</v>
+        <v>-3.1522</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3075</v>
+        <v>-1.7526</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.4126</v>
+        <v>-1.3997</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6805</v>
+        <v>1.3658</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8147</v>
+        <v>1.3658</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1786</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7984</v>
+        <v>0.5825</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3802</v>
+        <v>-0.0044</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.639</v>
+        <v>-1.2472</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.3856</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. YUSTA</t>
+          <t>M. SPISSU</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.8419</v>
+        <v>-2.7737</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.4835</v>
+        <v>-2.2634</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3584</v>
+        <v>-0.5103</v>
       </c>
       <c r="G22" t="n">
-        <v>-6.1279</v>
+        <v>-2.9887</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.4472</v>
+        <v>-0.2846</v>
       </c>
       <c r="I22" t="n">
-        <v>-4.6807</v>
+        <v>-2.7041</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.3919</v>
+        <v>-0.4117</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.2811</v>
+        <v>0.5204</v>
       </c>
       <c r="L22" t="n">
-        <v>-3.1108</v>
+        <v>-0.9320000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.7361</v>
+        <v>-2.577</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1662</v>
+        <v>-0.805</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.5699</v>
+        <v>-1.772</v>
       </c>
       <c r="P22" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R22" t="n">
-        <v>3.4025</v>
+        <v>3.1868</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2686</v>
+        <v>0.6119</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1693</v>
+        <v>0.4246</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0992</v>
+        <v>0.1873</v>
       </c>
       <c r="V22" t="n">
-        <v>1.4205</v>
+        <v>-1.3074</v>
       </c>
       <c r="W22" t="n">
-        <v>2.3461</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.9256</v>
+        <v>-1.3074</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. SPISSU</t>
+          <t>S. YUSTA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9663</v>
+        <v>-3.1249</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8171</v>
+        <v>-3.063</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1492</v>
+        <v>-0.0619</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.985</v>
+        <v>-6.1368</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2901</v>
+        <v>-1.4502</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.6949</v>
+        <v>-4.6866</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.3794</v>
+        <v>-3.4295</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5296999999999999</v>
+        <v>-0.3005</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.9091</v>
+        <v>-3.129</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.6056</v>
+        <v>-2.7073</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8198</v>
+        <v>-1.1497</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.7858</v>
+        <v>-1.5576</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>3.1757</v>
+        <v>3.4145</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5774</v>
+        <v>0.4575</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1693</v>
+        <v>0.3061</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.408</v>
+        <v>0.1513</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.3112</v>
+        <v>1.4163</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.3367</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.3112</v>
+        <v>-0.9204</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.2867</v>
+        <v>-3.6932</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.3143</v>
+        <v>0.1317</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.9724</v>
+        <v>-3.8249</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.8848</v>
+        <v>-1.8896</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6955</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.5803</v>
+        <v>-2.5847</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8119</v>
+        <v>0.7904</v>
       </c>
       <c r="K24" t="n">
-        <v>1.9395</v>
+        <v>1.9305</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.1276</v>
+        <v>-1.1401</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.6966</v>
+        <v>-2.68</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.244</v>
+        <v>-1.2355</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.4526</v>
+        <v>-1.4446</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0144</v>
+        <v>-0.4182</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5383</v>
+        <v>-0.0653</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4761</v>
+        <v>-0.3529</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W24" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.6497</v>
+        <v>-5.3565</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.8569</v>
+        <v>-2.5164</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.7928</v>
+        <v>-2.8402</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.9956</v>
+        <v>-2.9927</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.5988</v>
+        <v>-1.597</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.3967</v>
+        <v>-1.3957</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.4661</v>
+        <v>-1.4731</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.7171</v>
+        <v>-0.7207</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.5294</v>
+        <v>-1.5196</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.8817</v>
+        <v>-0.8763</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6433</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R25" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2686</v>
+        <v>0.0232</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4174</v>
+        <v>-0.0629</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1488</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.4783</v>
+        <v>-1.4764</v>
       </c>
       <c r="W25" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.5454</v>
+        <v>-7.7048</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.5292</v>
+        <v>-4.5524</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.0162</v>
+        <v>-3.1524</v>
       </c>
       <c r="G26" t="n">
-        <v>-3.8895</v>
+        <v>-3.887</v>
       </c>
       <c r="H26" t="n">
-        <v>-3.0605</v>
+        <v>-3.0589</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.829</v>
+        <v>-0.8282</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.0784</v>
+        <v>-1.0912</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.4861</v>
+        <v>-1.4931</v>
       </c>
       <c r="L26" t="n">
-        <v>0.4078</v>
+        <v>0.4019</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.8112</v>
+        <v>-2.7959</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.5744</v>
+        <v>-1.5658</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.2368</v>
+        <v>-1.2301</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q26" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R26" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S26" t="n">
-        <v>0.3856</v>
+        <v>0.2309</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.0484</v>
+        <v>-0.0468</v>
       </c>
       <c r="U26" t="n">
-        <v>0.434</v>
+        <v>0.2777</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-27.3025</v>
+        <v>-25.7268</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.927500000000001</v>
+        <v>-4.2517</v>
       </c>
       <c r="F27" t="n">
-        <v>-23.3748</v>
+        <v>-21.4751</v>
       </c>
       <c r="G27" t="n">
-        <v>-23.6178</v>
+        <v>-23.661</v>
       </c>
       <c r="H27" t="n">
-        <v>-8.4908</v>
+        <v>-8.541499999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>-15.127</v>
+        <v>-15.1193</v>
       </c>
       <c r="J27" t="n">
-        <v>2.893399999999999</v>
+        <v>2.6243</v>
       </c>
       <c r="K27" t="n">
-        <v>1.828</v>
+        <v>1.6607</v>
       </c>
       <c r="L27" t="n">
-        <v>1.0656</v>
+        <v>0.9636999999999996</v>
       </c>
       <c r="M27" t="n">
-        <v>-26.5113</v>
+        <v>-26.2853</v>
       </c>
       <c r="N27" t="n">
-        <v>-10.319</v>
+        <v>-10.2023</v>
       </c>
       <c r="O27" t="n">
-        <v>-16.1921</v>
+        <v>-16.083</v>
       </c>
       <c r="P27" t="n">
-        <v>1.1343</v>
+        <v>1.1383</v>
       </c>
       <c r="Q27" t="n">
-        <v>-17.0126</v>
+        <v>-17.0726</v>
       </c>
       <c r="R27" t="n">
-        <v>18.1467</v>
+        <v>18.2106</v>
       </c>
       <c r="S27" t="n">
-        <v>2.283399999999999</v>
+        <v>3.8777</v>
       </c>
       <c r="T27" t="n">
-        <v>3.5389</v>
+        <v>3.572999999999999</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.2552</v>
+        <v>0.3046</v>
       </c>
       <c r="V27" t="n">
-        <v>-7.102399999999999</v>
+        <v>-7.0816</v>
       </c>
       <c r="W27" t="n">
-        <v>6.6525</v>
+        <v>6.6232</v>
       </c>
       <c r="X27" t="n">
-        <v>-13.755</v>
+        <v>-13.7047</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104628_W19.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104628_W19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104628_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104628_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104628_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104628_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104628_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104628_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104628_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104628_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104628_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104628_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104628_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104628_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-6.6231</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.7625999999999999</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104628_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.3074</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104628_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104628_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104628_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104628_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.8521</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104628_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104628_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.3074</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104628_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.9204</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104628_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104628_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104628_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104628_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-13.7047</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
